--- a/Comparativa Exhaustiva de Agentes y ADEs 2026.xlsx
+++ b/Comparativa Exhaustiva de Agentes y ADEs 2026.xlsx
@@ -1,49 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ESTUDIANTES\Downloads\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{31B20AC5-8897-47D5-9F69-680048626E35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
   <sheets>
-    <sheet name="1_ADEs_Orquestadores" sheetId="1" r:id="rId1"/>
-    <sheet name="2_Harnesses_CLI" sheetId="2" r:id="rId2"/>
-    <sheet name="3_Agent_OS_Plataformas" sheetId="3" r:id="rId3"/>
-    <sheet name="4_Agentes_E2E_Cloud" sheetId="4" r:id="rId4"/>
-    <sheet name="5_Agentic_IDEs" sheetId="5" r:id="rId5"/>
-    <sheet name="6_Explicacion_Pedagogica" sheetId="6" r:id="rId6"/>
-    <sheet name="7_Detalle_de_Medidas" sheetId="7" r:id="rId7"/>
-    <sheet name="8_Capacidades_Ventajas_Desventa" sheetId="8" r:id="rId8"/>
+    <sheet state="visible" name="1_ADEs_Orquestadores" sheetId="1" r:id="rId5"/>
+    <sheet state="visible" name="2_Harnesses_CLI" sheetId="2" r:id="rId6"/>
+    <sheet state="visible" name="3_Agent_OS_Plataformas" sheetId="3" r:id="rId7"/>
+    <sheet state="visible" name="4_Agentes_E2E_Cloud" sheetId="4" r:id="rId8"/>
+    <sheet state="visible" name="5_Agentic_IDEs" sheetId="5" r:id="rId9"/>
+    <sheet state="visible" name="6_Explicacion_Pedagogica" sheetId="6" r:id="rId10"/>
+    <sheet state="visible" name="7_Detalle_de_Medidas" sheetId="7" r:id="rId11"/>
+    <sheet state="visible" name="8_Capacidades_Ventajas_Desventa" sheetId="8" r:id="rId12"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="430" uniqueCount="323">
   <si>
     <t>Puesto</t>
   </si>
@@ -103,6 +78,9 @@
   </si>
   <si>
     <t>Auto-aprendizaje con habilidades dinámicas persistentes</t>
+  </si>
+  <si>
+    <t>Contexto masivo y artefactos visuales</t>
   </si>
   <si>
     <t>Goose (Block)</t>
@@ -1014,48 +992,36 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <fonts count="3">
     <font>
-      <sz val="10"/>
+      <sz val="10.0"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="11.0"/>
       <color rgb="FFFFFFFF"/>
       <name val="Montserrat"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="10.0"/>
       <color rgb="FF181B20"/>
       <name val="Roboto"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
+      <patternFill patternType="lightGray"/>
     </fill>
   </fills>
   <borders count="2">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+    <border/>
     <border>
       <left style="thin">
         <color rgb="FF73777E"/>
@@ -1069,290 +1035,157 @@
       <bottom style="thin">
         <color rgb="FF73777E"/>
       </bottom>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="10">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+  <cellXfs count="9">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="9" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf quotePrefix="1" borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle xfId="0" name="Normal" builtinId="0"/>
   </cellStyles>
-  <dxfs count="24">
+  <dxfs count="4">
     <dxf>
+      <font/>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+      <border/>
+    </dxf>
+    <dxf>
+      <font/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF37608F"/>
+          <bgColor rgb="FF37608F"/>
+        </patternFill>
+      </fill>
+      <border/>
+    </dxf>
+    <dxf>
+      <font/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF7F9FF"/>
+          <bgColor rgb="FFF7F9FF"/>
+        </patternFill>
+      </fill>
+      <border/>
+    </dxf>
+    <dxf>
+      <font/>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFFFFFFF"/>
           <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF7F9FF"/>
-          <bgColor rgb="FFF7F9FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF37608F"/>
-          <bgColor rgb="FF37608F"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF7F9FF"/>
-          <bgColor rgb="FFF7F9FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF37608F"/>
-          <bgColor rgb="FF37608F"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF7F9FF"/>
-          <bgColor rgb="FFF7F9FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF37608F"/>
-          <bgColor rgb="FF37608F"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF7F9FF"/>
-          <bgColor rgb="FFF7F9FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF37608F"/>
-          <bgColor rgb="FF37608F"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF7F9FF"/>
-          <bgColor rgb="FFF7F9FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF37608F"/>
-          <bgColor rgb="FF37608F"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF7F9FF"/>
-          <bgColor rgb="FFF7F9FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF37608F"/>
-          <bgColor rgb="FF37608F"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF7F9FF"/>
-          <bgColor rgb="FFF7F9FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF37608F"/>
-          <bgColor rgb="FF37608F"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF7F9FF"/>
-          <bgColor rgb="FFF7F9FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF37608F"/>
-          <bgColor rgb="FF37608F"/>
-        </patternFill>
-      </fill>
+      <border/>
     </dxf>
   </dxfs>
   <tableStyles count="8">
-    <tableStyle name="3_Agent_OS_Plataformas-style" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="headerRow" dxfId="23"/>
-      <tableStyleElement type="firstRowStripe" dxfId="22"/>
-      <tableStyleElement type="secondRowStripe" dxfId="21"/>
+    <tableStyle count="3" pivot="0" name="3_Agent_OS_Plataformas-style">
+      <tableStyleElement dxfId="1" type="headerRow"/>
+      <tableStyleElement dxfId="2" type="firstRowStripe"/>
+      <tableStyleElement dxfId="3" type="secondRowStripe"/>
     </tableStyle>
-    <tableStyle name="1_ADEs_Orquestadores-style" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
-      <tableStyleElement type="headerRow" dxfId="20"/>
-      <tableStyleElement type="firstRowStripe" dxfId="19"/>
-      <tableStyleElement type="secondRowStripe" dxfId="18"/>
+    <tableStyle count="3" pivot="0" name="1_ADEs_Orquestadores-style">
+      <tableStyleElement dxfId="1" type="headerRow"/>
+      <tableStyleElement dxfId="2" type="firstRowStripe"/>
+      <tableStyleElement dxfId="3" type="secondRowStripe"/>
     </tableStyle>
-    <tableStyle name="4_Agentes_E2E_Cloud-style" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF02000000}">
-      <tableStyleElement type="headerRow" dxfId="17"/>
-      <tableStyleElement type="firstRowStripe" dxfId="16"/>
-      <tableStyleElement type="secondRowStripe" dxfId="15"/>
+    <tableStyle count="3" pivot="0" name="4_Agentes_E2E_Cloud-style">
+      <tableStyleElement dxfId="1" type="headerRow"/>
+      <tableStyleElement dxfId="2" type="firstRowStripe"/>
+      <tableStyleElement dxfId="3" type="secondRowStripe"/>
     </tableStyle>
-    <tableStyle name="2_Harnesses_CLI-style" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF03000000}">
-      <tableStyleElement type="headerRow" dxfId="14"/>
-      <tableStyleElement type="firstRowStripe" dxfId="13"/>
-      <tableStyleElement type="secondRowStripe" dxfId="12"/>
+    <tableStyle count="3" pivot="0" name="2_Harnesses_CLI-style">
+      <tableStyleElement dxfId="1" type="headerRow"/>
+      <tableStyleElement dxfId="2" type="firstRowStripe"/>
+      <tableStyleElement dxfId="3" type="secondRowStripe"/>
     </tableStyle>
-    <tableStyle name="5_Agentic_IDEs-style" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF04000000}">
-      <tableStyleElement type="headerRow" dxfId="11"/>
-      <tableStyleElement type="firstRowStripe" dxfId="10"/>
-      <tableStyleElement type="secondRowStripe" dxfId="9"/>
+    <tableStyle count="3" pivot="0" name="5_Agentic_IDEs-style">
+      <tableStyleElement dxfId="1" type="headerRow"/>
+      <tableStyleElement dxfId="2" type="firstRowStripe"/>
+      <tableStyleElement dxfId="3" type="secondRowStripe"/>
     </tableStyle>
-    <tableStyle name="6_Explicacion_Pedagogica-style" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF05000000}">
-      <tableStyleElement type="headerRow" dxfId="8"/>
-      <tableStyleElement type="firstRowStripe" dxfId="7"/>
-      <tableStyleElement type="secondRowStripe" dxfId="6"/>
+    <tableStyle count="3" pivot="0" name="6_Explicacion_Pedagogica-style">
+      <tableStyleElement dxfId="1" type="headerRow"/>
+      <tableStyleElement dxfId="2" type="firstRowStripe"/>
+      <tableStyleElement dxfId="3" type="secondRowStripe"/>
     </tableStyle>
-    <tableStyle name="7_Detalle_de_Medidas-style" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF06000000}">
-      <tableStyleElement type="headerRow" dxfId="5"/>
-      <tableStyleElement type="firstRowStripe" dxfId="4"/>
-      <tableStyleElement type="secondRowStripe" dxfId="3"/>
+    <tableStyle count="3" pivot="0" name="7_Detalle_de_Medidas-style">
+      <tableStyleElement dxfId="1" type="headerRow"/>
+      <tableStyleElement dxfId="2" type="firstRowStripe"/>
+      <tableStyleElement dxfId="3" type="secondRowStripe"/>
     </tableStyle>
-    <tableStyle name="8_Capacidades_Ventajas_Desventa-style" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF07000000}">
-      <tableStyleElement type="headerRow" dxfId="2"/>
-      <tableStyleElement type="firstRowStripe" dxfId="1"/>
-      <tableStyleElement type="secondRowStripe" dxfId="0"/>
+    <tableStyle count="3" pivot="0" name="8_Capacidades_Ventajas_Desventa-style">
+      <tableStyleElement dxfId="1" type="headerRow"/>
+      <tableStyleElement dxfId="2" type="firstRowStripe"/>
+      <tableStyleElement dxfId="3" type="secondRowStripe"/>
     </tableStyle>
   </tableStyles>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1360,134 +1193,134 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table_2" displayName="Table_2" ref="A1:J7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:J7" displayName="Table_2" name="Table_2" id="2">
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Puesto"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Herramienta"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="C1 (SWE 20%)"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="C2 (Autonomía 15%)"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="C3 (Coste 15%)"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="C4 (Aislamiento 15%)"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="C5 (Visual 15%)"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="C6 (Herramientas 20%)"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Puntuación Global"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Característica Clave"/>
+    <tableColumn name="Puesto" id="1"/>
+    <tableColumn name="Herramienta" id="2"/>
+    <tableColumn name="C1 (SWE 20%)" id="3"/>
+    <tableColumn name="C2 (Autonomía 15%)" id="4"/>
+    <tableColumn name="C3 (Coste 15%)" id="5"/>
+    <tableColumn name="C4 (Aislamiento 15%)" id="6"/>
+    <tableColumn name="C5 (Visual 15%)" id="7"/>
+    <tableColumn name="C6 (Herramientas 20%)" id="8"/>
+    <tableColumn name="Puntuación Global" id="9"/>
+    <tableColumn name="Característica Clave" id="10"/>
   </tableColumns>
-  <tableStyleInfo name="1_ADEs_Orquestadores-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="1_ADEs_Orquestadores-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Table_4" displayName="Table_4" ref="A1:J14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:J14" displayName="Table_4" name="Table_4" id="4">
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Puesto"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Herramienta"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="C1 (SWE 20%)"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="C2 (Autonomía 15%)"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="C3 (Coste 15%)"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="C4 (Aislamiento 15%)"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="C5 (Visual 15%)"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="C6 (Herramientas 20%)"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Puntuación Global"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="Característica Clave"/>
+    <tableColumn name="Puesto" id="1"/>
+    <tableColumn name="Herramienta" id="2"/>
+    <tableColumn name="C1 (SWE 20%)" id="3"/>
+    <tableColumn name="C2 (Autonomía 15%)" id="4"/>
+    <tableColumn name="C3 (Coste 15%)" id="5"/>
+    <tableColumn name="C4 (Aislamiento 15%)" id="6"/>
+    <tableColumn name="C5 (Visual 15%)" id="7"/>
+    <tableColumn name="C6 (Herramientas 20%)" id="8"/>
+    <tableColumn name="Puntuación Global" id="9"/>
+    <tableColumn name="Característica Clave" id="10"/>
   </tableColumns>
-  <tableStyleInfo name="2_Harnesses_CLI-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="2_Harnesses_CLI-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Table_1" displayName="Table_1" ref="A1:J6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:J6" displayName="Table_1" name="Table_1" id="1">
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Puesto"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Herramienta"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="C1 (SWE 20%)"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="C2 (Autonomía 15%)"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="C3 (Coste 15%)"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="C4 (Aislamiento 15%)"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0200-000007000000}" name="C5 (Visual 15%)"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0200-000008000000}" name="C6 (Herramientas 20%)"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0200-000009000000}" name="Puntuación Global"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0200-00000A000000}" name="Característica Clave"/>
+    <tableColumn name="Puesto" id="1"/>
+    <tableColumn name="Herramienta" id="2"/>
+    <tableColumn name="C1 (SWE 20%)" id="3"/>
+    <tableColumn name="C2 (Autonomía 15%)" id="4"/>
+    <tableColumn name="C3 (Coste 15%)" id="5"/>
+    <tableColumn name="C4 (Aislamiento 15%)" id="6"/>
+    <tableColumn name="C5 (Visual 15%)" id="7"/>
+    <tableColumn name="C6 (Herramientas 20%)" id="8"/>
+    <tableColumn name="Puntuación Global" id="9"/>
+    <tableColumn name="Característica Clave" id="10"/>
   </tableColumns>
-  <tableStyleInfo name="3_Agent_OS_Plataformas-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="3_Agent_OS_Plataformas-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="Table_3" displayName="Table_3" ref="A1:J5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:J5" displayName="Table_3" name="Table_3" id="3">
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="Puesto"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="Herramienta"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="C1 (SWE 20%)"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="C2 (Autonomía 15%)"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0300-000005000000}" name="C3 (Coste 15%)"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0300-000006000000}" name="C4 (Aislamiento 15%)"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0300-000007000000}" name="C5 (Visual 15%)"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0300-000008000000}" name="C6 (Herramientas 20%)"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0300-000009000000}" name="Puntuación Global"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0300-00000A000000}" name="Característica Clave"/>
+    <tableColumn name="Puesto" id="1"/>
+    <tableColumn name="Herramienta" id="2"/>
+    <tableColumn name="C1 (SWE 20%)" id="3"/>
+    <tableColumn name="C2 (Autonomía 15%)" id="4"/>
+    <tableColumn name="C3 (Coste 15%)" id="5"/>
+    <tableColumn name="C4 (Aislamiento 15%)" id="6"/>
+    <tableColumn name="C5 (Visual 15%)" id="7"/>
+    <tableColumn name="C6 (Herramientas 20%)" id="8"/>
+    <tableColumn name="Puntuación Global" id="9"/>
+    <tableColumn name="Característica Clave" id="10"/>
   </tableColumns>
-  <tableStyleInfo name="4_Agentes_E2E_Cloud-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="4_Agentes_E2E_Cloud-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="Table_5" displayName="Table_5" ref="A1:J9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:J9" displayName="Table_5" name="Table_5" id="5">
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="Puesto"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="Herramienta"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" name="C1 (SWE 20%)"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" name="C2 (Autonomía 15%)"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0400-000005000000}" name="C3 (Coste 15%)"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0400-000006000000}" name="C4 (Aislamiento 15%)"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0400-000007000000}" name="C5 (Visual 15%)"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0400-000008000000}" name="C6 (Herramientas 20%)"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0400-000009000000}" name="Puntuación Global"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0400-00000A000000}" name="Característica Clave"/>
+    <tableColumn name="Puesto" id="1"/>
+    <tableColumn name="Herramienta" id="2"/>
+    <tableColumn name="C1 (SWE 20%)" id="3"/>
+    <tableColumn name="C2 (Autonomía 15%)" id="4"/>
+    <tableColumn name="C3 (Coste 15%)" id="5"/>
+    <tableColumn name="C4 (Aislamiento 15%)" id="6"/>
+    <tableColumn name="C5 (Visual 15%)" id="7"/>
+    <tableColumn name="C6 (Herramientas 20%)" id="8"/>
+    <tableColumn name="Puntuación Global" id="9"/>
+    <tableColumn name="Característica Clave" id="10"/>
   </tableColumns>
-  <tableStyleInfo name="5_Agentic_IDEs-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="5_Agentic_IDEs-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="Table_6" displayName="Table_6" ref="A1:C10">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:C10" displayName="Table_6" name="Table_6" id="6">
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" name="Capa Arquitectónica"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0500-000002000000}" name="Descripción"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0500-000003000000}" name="Ejemplos"/>
+    <tableColumn name="Capa Arquitectónica" id="1"/>
+    <tableColumn name="Descripción" id="2"/>
+    <tableColumn name="Ejemplos" id="3"/>
   </tableColumns>
-  <tableStyleInfo name="6_Explicacion_Pedagogica-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="6_Explicacion_Pedagogica-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{00000000-000C-0000-FFFF-FFFF06000000}" name="Table_7" displayName="Table_7" ref="A1:C10">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:C10" displayName="Table_7" name="Table_7" id="7">
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0600-000001000000}" name="Medida"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0600-000002000000}" name="Peso"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0600-000003000000}" name="Definición"/>
+    <tableColumn name="Medida" id="1"/>
+    <tableColumn name="Peso" id="2"/>
+    <tableColumn name="Definición" id="3"/>
   </tableColumns>
-  <tableStyleInfo name="7_Detalle_de_Medidas-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="7_Detalle_de_Medidas-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{00000000-000C-0000-FFFF-FFFF07000000}" name="Table_8" displayName="Table_8" ref="A1:G37">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:G37" displayName="Table_8" name="Table_8" id="8">
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0700-000001000000}" name="Herramienta"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0700-000002000000}" name="Categoría"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0700-000003000000}" name="Desarrollador / Origen"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0700-000004000000}" name="Capacidades Principales"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0700-000005000000}" name="Características Clave"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0700-000006000000}" name="Ventajas Principales"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0700-000007000000}" name="Desventajas / Limitaciones"/>
+    <tableColumn name="Herramienta" id="1"/>
+    <tableColumn name="Categoría" id="2"/>
+    <tableColumn name="Desarrollador / Origen" id="3"/>
+    <tableColumn name="Capacidades Principales" id="4"/>
+    <tableColumn name="Características Clave" id="5"/>
+    <tableColumn name="Ventajas Principales" id="6"/>
+    <tableColumn name="Desventajas / Limitaciones" id="7"/>
   </tableColumns>
-  <tableStyleInfo name="8_Capacidades_Ventajas_Desventa-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="8_Capacidades_Ventajas_Desventa-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
 </table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -1677,32 +1510,29 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="6.5703125" customWidth="1"/>
-    <col min="2" max="2" width="16.7109375" customWidth="1"/>
-    <col min="3" max="3" width="12.42578125" customWidth="1"/>
-    <col min="4" max="4" width="17.42578125" customWidth="1"/>
-    <col min="5" max="5" width="13.42578125" customWidth="1"/>
-    <col min="6" max="6" width="18.28515625" customWidth="1"/>
-    <col min="7" max="7" width="13.5703125" customWidth="1"/>
-    <col min="8" max="8" width="19.5703125" customWidth="1"/>
-    <col min="9" max="9" width="15.5703125" customWidth="1"/>
-    <col min="10" max="10" width="30.42578125" customWidth="1"/>
+    <col customWidth="1" min="1" max="1" width="6.63"/>
+    <col customWidth="1" min="2" max="2" width="16.75"/>
+    <col customWidth="1" min="3" max="3" width="12.38"/>
+    <col customWidth="1" min="4" max="4" width="17.38"/>
+    <col customWidth="1" min="5" max="5" width="13.38"/>
+    <col customWidth="1" min="6" max="6" width="18.25"/>
+    <col customWidth="1" min="7" max="7" width="13.63"/>
+    <col customWidth="1" min="8" max="8" width="19.63"/>
+    <col customWidth="1" min="9" max="9" width="15.63"/>
+    <col customWidth="1" min="10" max="10" width="30.38"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1734,58 +1564,50 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2" s="9">
-        <f t="shared" ref="A2:J7" si="0">ROW()-1</f>
+    <row r="2">
+      <c r="A2" s="2">
+        <f t="shared" ref="A2:A7" si="1">ROW()-1</f>
         <v>1</v>
       </c>
-      <c r="B2" s="9">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="C2" s="9">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="D2" s="9">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="E2" s="9">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="F2" s="9">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="G2" s="9">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H2" s="9">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="I2" s="9">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="J2" s="9">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="2">
+        <v>9.2</v>
+      </c>
+      <c r="D2" s="2">
+        <v>9.0</v>
+      </c>
+      <c r="E2" s="2">
+        <v>9.4</v>
+      </c>
+      <c r="F2" s="2">
+        <v>9.2</v>
+      </c>
+      <c r="G2" s="2">
+        <v>9.5</v>
+      </c>
+      <c r="H2" s="2">
+        <v>9.2</v>
+      </c>
+      <c r="I2" s="4">
+        <f t="shared" ref="I2:I7" si="2">(C2*0.2)+(D2*0.15)+(E2*0.15)+(F2*0.15)+(G2*0.15)+(H2*0.2)</f>
+        <v>9.245</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C3" s="2">
-        <v>8.1999999999999993</v>
+        <v>8.2</v>
       </c>
       <c r="D3" s="2">
         <v>8.5</v>
@@ -1794,7 +1616,7 @@
         <v>7.8</v>
       </c>
       <c r="F3" s="2">
-        <v>9.8000000000000007</v>
+        <v>9.8</v>
       </c>
       <c r="G3" s="2">
         <v>9.6</v>
@@ -1803,100 +1625,100 @@
         <v>9.4</v>
       </c>
       <c r="I3" s="4">
-        <f t="shared" ref="I2:I7" si="1">(C3*0.2)+(D3*0.15)+(E3*0.15)+(F3*0.15)+(G3*0.15)+(H3*0.2)</f>
+        <f t="shared" si="2"/>
         <v>8.875</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C4" s="2">
         <v>8.4</v>
       </c>
       <c r="D4" s="2">
-        <v>8.8000000000000007</v>
+        <v>8.8</v>
       </c>
       <c r="E4" s="2">
-        <v>9.1999999999999993</v>
+        <v>9.2</v>
       </c>
       <c r="F4" s="2">
-        <v>8.8000000000000007</v>
+        <v>8.8</v>
       </c>
       <c r="G4" s="2">
-        <v>9.3000000000000007</v>
+        <v>9.3</v>
       </c>
       <c r="H4" s="2">
         <v>8.5</v>
       </c>
       <c r="I4" s="4">
+        <f t="shared" si="2"/>
+        <v>8.795</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2">
         <f t="shared" si="1"/>
-        <v>8.7950000000000017</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A5" s="2">
-        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C5" s="2">
         <v>8.5</v>
       </c>
       <c r="D5" s="2">
-        <v>8.8000000000000007</v>
+        <v>8.8</v>
       </c>
       <c r="E5" s="2">
-        <v>8</v>
+        <v>8.0</v>
       </c>
       <c r="F5" s="2">
         <v>8.5</v>
       </c>
       <c r="G5" s="2">
-        <v>9</v>
+        <v>9.0</v>
       </c>
       <c r="H5" s="2">
-        <v>9.1999999999999993</v>
+        <v>9.2</v>
       </c>
       <c r="I5" s="4">
+        <f t="shared" si="2"/>
+        <v>8.685</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4">
         <f t="shared" si="1"/>
-        <v>8.6850000000000005</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A6" s="4">
-        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C6" s="2">
-        <v>8</v>
+        <v>8.0</v>
       </c>
       <c r="D6" s="2">
         <v>8.5</v>
       </c>
       <c r="E6" s="2">
-        <v>8.1999999999999993</v>
+        <v>8.2</v>
       </c>
       <c r="F6" s="2">
-        <v>8.8000000000000007</v>
+        <v>8.8</v>
       </c>
       <c r="G6" s="2">
         <v>8.5</v>
@@ -1905,76 +1727,75 @@
         <v>8.6</v>
       </c>
       <c r="I6" s="4">
+        <f t="shared" si="2"/>
+        <v>8.42</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4">
         <f t="shared" si="1"/>
-        <v>8.42</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A7" s="4">
-        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C7" s="2">
         <v>8.5</v>
       </c>
       <c r="D7" s="2">
-        <v>8</v>
+        <v>8.0</v>
       </c>
       <c r="E7" s="2">
         <v>7.6</v>
       </c>
       <c r="F7" s="2">
-        <v>8.8000000000000007</v>
+        <v>8.8</v>
       </c>
       <c r="G7" s="2">
-        <v>9</v>
+        <v>9.0</v>
       </c>
       <c r="H7" s="2">
         <v>8.4</v>
       </c>
       <c r="I7" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>8.39</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId3"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="6.5703125" customWidth="1"/>
-    <col min="2" max="2" width="18.7109375" customWidth="1"/>
-    <col min="3" max="3" width="12.42578125" customWidth="1"/>
-    <col min="4" max="4" width="17.42578125" customWidth="1"/>
-    <col min="5" max="5" width="13.42578125" customWidth="1"/>
-    <col min="6" max="6" width="18.28515625" customWidth="1"/>
-    <col min="7" max="7" width="13.5703125" customWidth="1"/>
-    <col min="8" max="8" width="19.5703125" customWidth="1"/>
-    <col min="9" max="9" width="15.5703125" customWidth="1"/>
-    <col min="10" max="10" width="34" customWidth="1"/>
+    <col customWidth="1" min="1" max="1" width="6.63"/>
+    <col customWidth="1" min="2" max="2" width="18.75"/>
+    <col customWidth="1" min="3" max="3" width="12.38"/>
+    <col customWidth="1" min="4" max="4" width="17.38"/>
+    <col customWidth="1" min="5" max="5" width="13.38"/>
+    <col customWidth="1" min="6" max="6" width="18.25"/>
+    <col customWidth="1" min="7" max="7" width="13.63"/>
+    <col customWidth="1" min="8" max="8" width="19.63"/>
+    <col customWidth="1" min="9" max="9" width="15.63"/>
+    <col customWidth="1" min="10" max="10" width="34.0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2006,124 +1827,124 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="2">
       <c r="A2" s="2">
-        <f t="shared" ref="A2:A14" si="0">ROW()-1</f>
+        <f t="shared" ref="A2:A14" si="1">ROW()-1</f>
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C2" s="2">
-        <v>9.3000000000000007</v>
+        <v>9.3</v>
       </c>
       <c r="D2" s="2">
         <v>8.4</v>
       </c>
       <c r="E2" s="2">
-        <v>8.8000000000000007</v>
+        <v>8.8</v>
       </c>
       <c r="F2" s="2">
-        <v>8</v>
+        <v>8.0</v>
       </c>
       <c r="G2" s="2">
-        <v>8.1999999999999993</v>
+        <v>8.2</v>
       </c>
       <c r="H2" s="2">
         <v>9.6</v>
       </c>
       <c r="I2" s="4">
-        <f t="shared" ref="I2:I14" si="1">(C2*0.2)+(D2*0.15)+(E2*0.15)+(F2*0.15)+(G2*0.15)+(H2*0.2)</f>
-        <v>8.7899999999999991</v>
+        <f t="shared" ref="I2:I14" si="2">(C2*0.2)+(D2*0.15)+(E2*0.15)+(F2*0.15)+(G2*0.15)+(H2*0.2)</f>
+        <v>8.79</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C3" s="2">
         <v>9.4</v>
       </c>
       <c r="D3" s="2">
-        <v>8.8000000000000007</v>
+        <v>8.8</v>
       </c>
       <c r="E3" s="2">
-        <v>8</v>
+        <v>8.0</v>
       </c>
       <c r="F3" s="2">
-        <v>8.8000000000000007</v>
+        <v>8.8</v>
       </c>
       <c r="G3" s="2">
-        <v>8.1999999999999993</v>
+        <v>8.2</v>
       </c>
       <c r="H3" s="2">
-        <v>9.1999999999999993</v>
+        <v>9.2</v>
       </c>
       <c r="I3" s="4">
+        <f t="shared" si="2"/>
+        <v>8.79</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2">
         <f t="shared" si="1"/>
-        <v>8.7899999999999991</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A4" s="2">
-        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C4" s="2">
         <v>9.6</v>
       </c>
       <c r="D4" s="2">
-        <v>8.8000000000000007</v>
+        <v>8.8</v>
       </c>
       <c r="E4" s="2">
-        <v>8.1999999999999993</v>
+        <v>8.2</v>
       </c>
       <c r="F4" s="2">
-        <v>8</v>
+        <v>8.0</v>
       </c>
       <c r="G4" s="2">
-        <v>8</v>
+        <v>8.0</v>
       </c>
       <c r="H4" s="2">
         <v>9.5</v>
       </c>
       <c r="I4" s="4">
+        <f t="shared" si="2"/>
+        <v>8.77</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2">
         <f t="shared" si="1"/>
-        <v>8.77</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A5" s="2">
-        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C5" s="2">
-        <v>8.8000000000000007</v>
+        <v>8.8</v>
       </c>
       <c r="D5" s="2">
         <v>8.6</v>
       </c>
       <c r="E5" s="2">
-        <v>9</v>
+        <v>9.0</v>
       </c>
       <c r="F5" s="2">
         <v>8.5</v>
@@ -2132,29 +1953,29 @@
         <v>6.5</v>
       </c>
       <c r="H5" s="2">
-        <v>9.8000000000000007</v>
+        <v>9.8</v>
       </c>
       <c r="I5" s="4">
+        <f t="shared" si="2"/>
+        <v>8.61</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2">
         <f t="shared" si="1"/>
-        <v>8.61</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A6" s="2">
-        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C6" s="2">
         <v>9.1</v>
       </c>
       <c r="D6" s="2">
-        <v>9.8000000000000007</v>
+        <v>9.8</v>
       </c>
       <c r="E6" s="2">
         <v>7.8</v>
@@ -2166,23 +1987,23 @@
         <v>6.5</v>
       </c>
       <c r="H6" s="2">
-        <v>9</v>
+        <v>9.0</v>
       </c>
       <c r="I6" s="4">
+        <f t="shared" si="2"/>
+        <v>8.405</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2">
         <f t="shared" si="1"/>
-        <v>8.4049999999999994</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A7" s="2">
-        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C7" s="2">
         <v>8.9</v>
@@ -2191,7 +2012,7 @@
         <v>8.5</v>
       </c>
       <c r="E7" s="2">
-        <v>8.8000000000000007</v>
+        <v>8.8</v>
       </c>
       <c r="F7" s="2">
         <v>7.8</v>
@@ -2200,94 +2021,94 @@
         <v>7.2</v>
       </c>
       <c r="H7" s="2">
-        <v>8.8000000000000007</v>
+        <v>8.8</v>
       </c>
       <c r="I7" s="4">
+        <f t="shared" si="2"/>
+        <v>8.385</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2">
         <f t="shared" si="1"/>
-        <v>8.3849999999999998</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A8" s="2">
-        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C8" s="2">
-        <v>8.6999999999999993</v>
+        <v>8.7</v>
       </c>
       <c r="D8" s="2">
-        <v>8</v>
+        <v>8.0</v>
       </c>
       <c r="E8" s="2">
         <v>9.9</v>
       </c>
       <c r="F8" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="G8" s="2">
+        <v>7.0</v>
+      </c>
+      <c r="H8" s="2">
+        <v>8.2</v>
+      </c>
+      <c r="I8" s="4">
+        <f t="shared" si="2"/>
+        <v>8.315</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2">
+        <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="G8" s="2">
-        <v>7</v>
-      </c>
-      <c r="H8" s="2">
-        <v>8.1999999999999993</v>
-      </c>
-      <c r="I8" s="4">
-        <f t="shared" si="1"/>
-        <v>8.3149999999999995</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A9" s="2">
-        <f t="shared" si="0"/>
-        <v>8</v>
-      </c>
       <c r="B9" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C9" s="2">
-        <v>9</v>
+        <v>9.0</v>
       </c>
       <c r="D9" s="2">
-        <v>8.1999999999999993</v>
+        <v>8.2</v>
       </c>
       <c r="E9" s="2">
-        <v>8</v>
+        <v>8.0</v>
       </c>
       <c r="F9" s="2">
-        <v>8</v>
+        <v>8.0</v>
       </c>
       <c r="G9" s="2">
         <v>7.5</v>
       </c>
       <c r="H9" s="2">
-        <v>8.1999999999999993</v>
+        <v>8.2</v>
       </c>
       <c r="I9" s="4">
+        <f t="shared" si="2"/>
+        <v>8.195</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2">
         <f t="shared" si="1"/>
-        <v>8.1950000000000003</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A10" s="2">
-        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C10" s="2">
-        <v>8.8000000000000007</v>
+        <v>8.8</v>
       </c>
       <c r="D10" s="2">
         <v>7.8</v>
@@ -2299,26 +2120,26 @@
         <v>7.5</v>
       </c>
       <c r="G10" s="2">
-        <v>6</v>
+        <v>6.0</v>
       </c>
       <c r="H10" s="2">
         <v>9.6</v>
       </c>
       <c r="I10" s="4">
+        <f t="shared" si="2"/>
+        <v>8.15</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2">
         <f t="shared" si="1"/>
-        <v>8.15</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A11" s="2">
-        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C11" s="2">
         <v>8.9</v>
@@ -2327,69 +2148,69 @@
         <v>7.5</v>
       </c>
       <c r="E11" s="2">
-        <v>8.8000000000000007</v>
+        <v>8.8</v>
       </c>
       <c r="F11" s="2">
-        <v>8</v>
+        <v>8.0</v>
       </c>
       <c r="G11" s="2">
         <v>5.5</v>
       </c>
       <c r="H11" s="2">
-        <v>8.8000000000000007</v>
+        <v>8.8</v>
       </c>
       <c r="I11" s="4">
+        <f t="shared" si="2"/>
+        <v>8.01</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2">
         <f t="shared" si="1"/>
-        <v>8.0100000000000016</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A12" s="2">
-        <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C12" s="2">
-        <v>9</v>
+        <v>9.0</v>
       </c>
       <c r="D12" s="2">
-        <v>8.1999999999999993</v>
+        <v>8.2</v>
       </c>
       <c r="E12" s="2">
         <v>9.5</v>
       </c>
       <c r="F12" s="2">
-        <v>7</v>
+        <v>7.0</v>
       </c>
       <c r="G12" s="2">
-        <v>6</v>
+        <v>6.0</v>
       </c>
       <c r="H12" s="2">
         <v>7.5</v>
       </c>
       <c r="I12" s="4">
+        <f t="shared" si="2"/>
+        <v>7.905</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4">
         <f t="shared" si="1"/>
-        <v>7.9049999999999994</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A13" s="4">
-        <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C13" s="2">
-        <v>8.8000000000000007</v>
+        <v>8.8</v>
       </c>
       <c r="D13" s="2">
         <v>7.8</v>
@@ -2401,32 +2222,32 @@
         <v>7.5</v>
       </c>
       <c r="G13" s="2">
-        <v>6</v>
+        <v>6.0</v>
       </c>
       <c r="H13" s="2">
         <v>6.8</v>
       </c>
       <c r="I13" s="4">
+        <f t="shared" si="2"/>
+        <v>7.59</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4">
         <f t="shared" si="1"/>
-        <v>7.5900000000000007</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A14" s="4">
-        <f t="shared" si="0"/>
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C14" s="2">
         <v>9.6</v>
       </c>
       <c r="D14" s="2">
-        <v>8</v>
+        <v>8.0</v>
       </c>
       <c r="E14" s="2">
         <v>6.8</v>
@@ -2435,48 +2256,47 @@
         <v>6.5</v>
       </c>
       <c r="G14" s="2">
-        <v>5</v>
+        <v>5.0</v>
       </c>
       <c r="H14" s="2">
         <v>8.5</v>
       </c>
       <c r="I14" s="4">
-        <f t="shared" si="1"/>
-        <v>7.5650000000000004</v>
+        <f t="shared" si="2"/>
+        <v>7.565</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId3"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="6.5703125" customWidth="1"/>
-    <col min="2" max="2" width="21.7109375" customWidth="1"/>
-    <col min="3" max="3" width="12.42578125" customWidth="1"/>
-    <col min="4" max="4" width="17.42578125" customWidth="1"/>
-    <col min="5" max="5" width="13.42578125" customWidth="1"/>
-    <col min="6" max="6" width="18.28515625" customWidth="1"/>
-    <col min="7" max="7" width="13.5703125" customWidth="1"/>
-    <col min="8" max="8" width="19.5703125" customWidth="1"/>
-    <col min="9" max="9" width="15.5703125" customWidth="1"/>
-    <col min="10" max="10" width="42.140625" customWidth="1"/>
+    <col customWidth="1" min="1" max="1" width="6.63"/>
+    <col customWidth="1" min="2" max="2" width="21.75"/>
+    <col customWidth="1" min="3" max="3" width="12.38"/>
+    <col customWidth="1" min="4" max="4" width="17.38"/>
+    <col customWidth="1" min="5" max="5" width="13.38"/>
+    <col customWidth="1" min="6" max="6" width="18.25"/>
+    <col customWidth="1" min="7" max="7" width="13.63"/>
+    <col customWidth="1" min="8" max="8" width="19.63"/>
+    <col customWidth="1" min="9" max="9" width="15.63"/>
+    <col customWidth="1" min="10" max="10" width="42.13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2508,9 +2328,9 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="2">
       <c r="A2" s="2">
-        <f t="shared" ref="A2:A6" si="0">ROW()-1</f>
+        <f t="shared" ref="A2:A6" si="1">ROW()-1</f>
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
@@ -2523,69 +2343,69 @@
         <v>9.6</v>
       </c>
       <c r="E2" s="2">
-        <v>9.3000000000000007</v>
+        <v>9.3</v>
       </c>
       <c r="F2" s="2">
-        <v>9</v>
+        <v>9.0</v>
       </c>
       <c r="G2" s="2">
-        <v>9.1999999999999993</v>
+        <v>9.2</v>
       </c>
       <c r="H2" s="2">
-        <v>9.6999999999999993</v>
+        <v>9.7</v>
       </c>
       <c r="I2" s="4">
-        <f t="shared" ref="I2:I6" si="1">(C2*0.2)+(D2*0.15)+(E2*0.15)+(F2*0.15)+(G2*0.15)+(H2*0.2)</f>
-        <v>9.1850000000000005</v>
+        <f t="shared" ref="I2:I6" si="2">(C2*0.2)+(D2*0.15)+(E2*0.15)+(F2*0.15)+(G2*0.15)+(H2*0.2)</f>
+        <v>9.185</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="3">
       <c r="A3" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>14</v>
       </c>
       <c r="C3" s="2">
-        <v>8.1999999999999993</v>
+        <v>8.2</v>
       </c>
       <c r="D3" s="2">
         <v>8.5</v>
       </c>
       <c r="E3" s="2">
-        <v>8.1999999999999993</v>
+        <v>8.2</v>
       </c>
       <c r="F3" s="2">
-        <v>8.1999999999999993</v>
+        <v>8.2</v>
       </c>
       <c r="G3" s="2">
-        <v>8.8000000000000007</v>
+        <v>8.8</v>
       </c>
       <c r="H3" s="2">
-        <v>9.8000000000000007</v>
+        <v>9.8</v>
       </c>
       <c r="I3" s="4">
-        <f t="shared" si="1"/>
-        <v>8.6549999999999994</v>
+        <f t="shared" si="2"/>
+        <v>8.655</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="4">
       <c r="A4" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C4" s="2">
-        <v>8</v>
+        <v>8.0</v>
       </c>
       <c r="D4" s="2">
         <v>8.4</v>
@@ -2594,41 +2414,41 @@
         <v>8.6</v>
       </c>
       <c r="F4" s="2">
-        <v>8.1999999999999993</v>
+        <v>8.2</v>
       </c>
       <c r="G4" s="2">
-        <v>9.1999999999999993</v>
+        <v>9.2</v>
       </c>
       <c r="H4" s="2">
-        <v>9.1999999999999993</v>
+        <v>9.2</v>
       </c>
       <c r="I4" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>8.6</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5">
       <c r="A5" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C5" s="2">
-        <v>8.3000000000000007</v>
+        <v>8.3</v>
       </c>
       <c r="D5" s="2">
-        <v>9</v>
+        <v>9.0</v>
       </c>
       <c r="E5" s="2">
         <v>8.4</v>
       </c>
       <c r="F5" s="2">
-        <v>8</v>
+        <v>8.0</v>
       </c>
       <c r="G5" s="2">
         <v>6.8</v>
@@ -2637,26 +2457,26 @@
         <v>9.4</v>
       </c>
       <c r="I5" s="4">
-        <f t="shared" si="1"/>
-        <v>8.370000000000001</v>
+        <f t="shared" si="2"/>
+        <v>8.37</v>
       </c>
       <c r="J5" s="3" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6">
       <c r="A6" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C6" s="2">
-        <v>8.1999999999999993</v>
+        <v>8.2</v>
       </c>
       <c r="D6" s="2">
-        <v>8</v>
+        <v>8.0</v>
       </c>
       <c r="E6" s="2">
         <v>8.4</v>
@@ -2668,45 +2488,44 @@
         <v>7.2</v>
       </c>
       <c r="H6" s="2">
-        <v>9.1999999999999993</v>
+        <v>9.2</v>
       </c>
       <c r="I6" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>8.19</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId3"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="6.5703125" customWidth="1"/>
-    <col min="2" max="2" width="15.5703125" customWidth="1"/>
-    <col min="3" max="3" width="12.42578125" customWidth="1"/>
-    <col min="4" max="4" width="17.42578125" customWidth="1"/>
-    <col min="5" max="5" width="13.42578125" customWidth="1"/>
-    <col min="6" max="6" width="18.28515625" customWidth="1"/>
-    <col min="7" max="7" width="13.5703125" customWidth="1"/>
-    <col min="8" max="8" width="19.5703125" customWidth="1"/>
-    <col min="9" max="9" width="15.5703125" customWidth="1"/>
-    <col min="10" max="10" width="30.5703125" customWidth="1"/>
+    <col customWidth="1" min="1" max="1" width="6.63"/>
+    <col customWidth="1" min="2" max="2" width="15.63"/>
+    <col customWidth="1" min="3" max="3" width="12.38"/>
+    <col customWidth="1" min="4" max="4" width="17.38"/>
+    <col customWidth="1" min="5" max="5" width="13.38"/>
+    <col customWidth="1" min="6" max="6" width="18.25"/>
+    <col customWidth="1" min="7" max="7" width="13.63"/>
+    <col customWidth="1" min="8" max="8" width="19.63"/>
+    <col customWidth="1" min="9" max="9" width="15.63"/>
+    <col customWidth="1" min="10" max="10" width="30.63"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2738,9 +2557,9 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="2">
       <c r="A2" s="2">
-        <f t="shared" ref="A2:A5" si="0">ROW()-1</f>
+        <f t="shared" ref="A2:A5" si="1">ROW()-1</f>
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
@@ -2750,103 +2569,103 @@
         <v>8.6</v>
       </c>
       <c r="D2" s="2">
-        <v>9.8000000000000007</v>
+        <v>9.8</v>
       </c>
       <c r="E2" s="2">
-        <v>7</v>
+        <v>7.0</v>
       </c>
       <c r="F2" s="2">
-        <v>9.8000000000000007</v>
+        <v>9.8</v>
       </c>
       <c r="G2" s="2">
         <v>9.4</v>
       </c>
       <c r="H2" s="2">
-        <v>8.8000000000000007</v>
+        <v>8.8</v>
       </c>
       <c r="I2" s="4">
-        <f t="shared" ref="I2:I5" si="1">(C2*0.2)+(D2*0.15)+(E2*0.15)+(F2*0.15)+(G2*0.15)+(H2*0.2)</f>
-        <v>8.8800000000000008</v>
+        <f t="shared" ref="I2:I5" si="2">(C2*0.2)+(D2*0.15)+(E2*0.15)+(F2*0.15)+(G2*0.15)+(H2*0.2)</f>
+        <v>8.88</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C3" s="2">
         <v>8.6</v>
       </c>
       <c r="D3" s="2">
-        <v>9</v>
+        <v>9.0</v>
       </c>
       <c r="E3" s="2">
         <v>7.2</v>
       </c>
       <c r="F3" s="2">
-        <v>9.1999999999999993</v>
+        <v>9.2</v>
       </c>
       <c r="G3" s="2">
-        <v>8</v>
+        <v>8.0</v>
       </c>
       <c r="H3" s="2">
         <v>9.4</v>
       </c>
       <c r="I3" s="4">
+        <f t="shared" si="2"/>
+        <v>8.61</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2">
         <f t="shared" si="1"/>
-        <v>8.6100000000000012</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A4" s="2">
-        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C4" s="2">
         <v>7.8</v>
       </c>
       <c r="D4" s="2">
-        <v>9.1999999999999993</v>
+        <v>9.2</v>
       </c>
       <c r="E4" s="2">
         <v>8.5</v>
       </c>
       <c r="F4" s="2">
-        <v>8.8000000000000007</v>
+        <v>8.8</v>
       </c>
       <c r="G4" s="2">
-        <v>9</v>
+        <v>9.0</v>
       </c>
       <c r="H4" s="2">
         <v>8.6</v>
       </c>
       <c r="I4" s="4">
+        <f t="shared" si="2"/>
+        <v>8.605</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2">
         <f t="shared" si="1"/>
-        <v>8.6050000000000004</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A5" s="2">
-        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C5" s="2">
         <v>8.9</v>
@@ -2864,45 +2683,44 @@
         <v>8.6</v>
       </c>
       <c r="H5" s="2">
-        <v>7</v>
+        <v>7.0</v>
       </c>
       <c r="I5" s="4">
-        <f t="shared" si="1"/>
-        <v>8.2949999999999999</v>
+        <f t="shared" si="2"/>
+        <v>8.295</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId3"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="6.5703125" customWidth="1"/>
-    <col min="2" max="2" width="18.140625" customWidth="1"/>
-    <col min="3" max="3" width="12.42578125" customWidth="1"/>
-    <col min="4" max="4" width="17.42578125" customWidth="1"/>
-    <col min="5" max="5" width="13.42578125" customWidth="1"/>
-    <col min="6" max="6" width="18.28515625" customWidth="1"/>
-    <col min="7" max="7" width="13.5703125" customWidth="1"/>
-    <col min="8" max="8" width="19.5703125" customWidth="1"/>
-    <col min="9" max="9" width="15.5703125" customWidth="1"/>
-    <col min="10" max="10" width="31.140625" customWidth="1"/>
+    <col customWidth="1" min="1" max="1" width="6.63"/>
+    <col customWidth="1" min="2" max="2" width="18.13"/>
+    <col customWidth="1" min="3" max="3" width="12.38"/>
+    <col customWidth="1" min="4" max="4" width="17.38"/>
+    <col customWidth="1" min="5" max="5" width="13.38"/>
+    <col customWidth="1" min="6" max="6" width="18.25"/>
+    <col customWidth="1" min="7" max="7" width="13.63"/>
+    <col customWidth="1" min="8" max="8" width="19.63"/>
+    <col customWidth="1" min="9" max="9" width="15.63"/>
+    <col customWidth="1" min="10" max="10" width="31.13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2934,19 +2752,19 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="2">
       <c r="A2" s="2">
-        <f t="shared" ref="A2:A9" si="0">ROW()-1</f>
+        <f t="shared" ref="A2:A9" si="1">ROW()-1</f>
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C2" s="2">
         <v>8.9</v>
       </c>
       <c r="D2" s="2">
-        <v>8.1999999999999993</v>
+        <v>8.2</v>
       </c>
       <c r="E2" s="2">
         <v>8.4</v>
@@ -2955,66 +2773,66 @@
         <v>7.8</v>
       </c>
       <c r="G2" s="2">
-        <v>9.1999999999999993</v>
+        <v>9.2</v>
       </c>
       <c r="H2" s="2">
         <v>9.5</v>
       </c>
       <c r="I2" s="4">
-        <f t="shared" ref="I2:I9" si="1">(C2*0.2)+(D2*0.15)+(E2*0.15)+(F2*0.15)+(G2*0.15)+(H2*0.2)</f>
-        <v>8.7199999999999989</v>
+        <f t="shared" ref="I2:I9" si="2">(C2*0.2)+(D2*0.15)+(E2*0.15)+(F2*0.15)+(G2*0.15)+(H2*0.2)</f>
+        <v>8.72</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C3" s="2">
         <v>8.9</v>
       </c>
       <c r="D3" s="2">
-        <v>8</v>
+        <v>8.0</v>
       </c>
       <c r="E3" s="2">
-        <v>8.1999999999999993</v>
+        <v>8.2</v>
       </c>
       <c r="F3" s="2">
         <v>7.5</v>
       </c>
       <c r="G3" s="2">
-        <v>9.1999999999999993</v>
+        <v>9.2</v>
       </c>
       <c r="H3" s="2">
         <v>9.6</v>
       </c>
       <c r="I3" s="4">
+        <f t="shared" si="2"/>
+        <v>8.635</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2">
         <f t="shared" si="1"/>
-        <v>8.6349999999999998</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A4" s="2">
-        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C4" s="2">
-        <v>8.1999999999999993</v>
+        <v>8.2</v>
       </c>
       <c r="D4" s="2">
-        <v>8</v>
+        <v>8.0</v>
       </c>
       <c r="E4" s="2">
         <v>9.6</v>
@@ -3023,29 +2841,29 @@
         <v>7.5</v>
       </c>
       <c r="G4" s="2">
-        <v>9.6999999999999993</v>
+        <v>9.7</v>
       </c>
       <c r="H4" s="2">
         <v>7.8</v>
       </c>
       <c r="I4" s="4">
+        <f t="shared" si="2"/>
+        <v>8.42</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2">
         <f t="shared" si="1"/>
-        <v>8.42</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A5" s="2">
-        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C5" s="2">
-        <v>8.8000000000000007</v>
+        <v>8.8</v>
       </c>
       <c r="D5" s="2">
         <v>7.5</v>
@@ -3060,57 +2878,57 @@
         <v>9.6</v>
       </c>
       <c r="H5" s="2">
-        <v>9</v>
+        <v>9.0</v>
       </c>
       <c r="I5" s="4">
+        <f t="shared" si="2"/>
+        <v>8.375</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2">
         <f t="shared" si="1"/>
-        <v>8.375</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A6" s="2">
-        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C6" s="2">
-        <v>8</v>
+        <v>8.0</v>
       </c>
       <c r="D6" s="2">
         <v>7.6</v>
       </c>
       <c r="E6" s="2">
-        <v>8.1999999999999993</v>
+        <v>8.2</v>
       </c>
       <c r="F6" s="2">
-        <v>8.8000000000000007</v>
+        <v>8.8</v>
       </c>
       <c r="G6" s="2">
-        <v>9.6999999999999993</v>
+        <v>9.7</v>
       </c>
       <c r="H6" s="2">
-        <v>8</v>
+        <v>8.0</v>
       </c>
       <c r="I6" s="4">
+        <f t="shared" si="2"/>
+        <v>8.345</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2">
         <f t="shared" si="1"/>
-        <v>8.3450000000000006</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A7" s="2">
-        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C7" s="2">
         <v>7.9</v>
@@ -3119,32 +2937,32 @@
         <v>7.5</v>
       </c>
       <c r="E7" s="2">
-        <v>8</v>
+        <v>8.0</v>
       </c>
       <c r="F7" s="2">
-        <v>8.1999999999999993</v>
+        <v>8.2</v>
       </c>
       <c r="G7" s="2">
-        <v>9.8000000000000007</v>
+        <v>9.8</v>
       </c>
       <c r="H7" s="2">
-        <v>8.1999999999999993</v>
+        <v>8.2</v>
       </c>
       <c r="I7" s="4">
+        <f t="shared" si="2"/>
+        <v>8.245</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2">
         <f t="shared" si="1"/>
-        <v>8.2449999999999992</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A8" s="2">
-        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C8" s="2">
         <v>8.6</v>
@@ -3156,7 +2974,7 @@
         <v>7.8</v>
       </c>
       <c r="F8" s="2">
-        <v>7</v>
+        <v>7.0</v>
       </c>
       <c r="G8" s="2">
         <v>9.5</v>
@@ -3165,20 +2983,20 @@
         <v>8.6</v>
       </c>
       <c r="I8" s="4">
+        <f t="shared" si="2"/>
+        <v>8.195</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4">
         <f t="shared" si="1"/>
-        <v>8.1950000000000003</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A9" s="4">
-        <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C9" s="2">
         <v>7.5</v>
@@ -3187,1157 +3005,1154 @@
         <v>6.5</v>
       </c>
       <c r="E9" s="2">
-        <v>8</v>
+        <v>8.0</v>
       </c>
       <c r="F9" s="2">
-        <v>7</v>
+        <v>7.0</v>
       </c>
       <c r="G9" s="2">
         <v>9.9</v>
       </c>
       <c r="H9" s="2">
-        <v>7</v>
+        <v>7.0</v>
       </c>
       <c r="I9" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>7.61</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId3"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="17.28515625" customWidth="1"/>
-    <col min="2" max="2" width="13" customWidth="1"/>
-    <col min="3" max="3" width="12.28515625" customWidth="1"/>
+    <col customWidth="1" min="1" max="1" width="17.25"/>
+    <col customWidth="1" min="2" max="2" width="13.0"/>
+    <col customWidth="1" min="3" max="3" width="12.25"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1">
       <c r="A1" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4" s="5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="5">
       <c r="A5" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6" s="5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="7">
       <c r="A7" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="8">
       <c r="A8" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="9">
       <c r="A9" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    </row>
+    <row r="10">
       <c r="A10" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId3"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="12.7109375" customWidth="1"/>
-    <col min="2" max="2" width="5" customWidth="1"/>
-    <col min="3" max="3" width="13" customWidth="1"/>
+    <col customWidth="1" min="1" max="1" width="12.75"/>
+    <col customWidth="1" min="2" max="2" width="5.0"/>
+    <col customWidth="1" min="3" max="3" width="13.0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1">
       <c r="A1" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" s="5" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B2" s="6">
         <v>0.2</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" s="5" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B3" s="6">
         <v>0.15</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4" s="5" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B4" s="6">
         <v>0.15</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="5">
       <c r="A5" s="5" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B5" s="6">
         <v>0.15</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6" s="5" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B6" s="6">
         <v>0.15</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="7">
       <c r="A7" s="5" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B7" s="6">
         <v>0.2</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="8">
       <c r="A8" s="7"/>
       <c r="B8" s="7"/>
       <c r="C8" s="5"/>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9">
       <c r="A9" s="5" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="8" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="10">
       <c r="A10" s="5" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B10" s="7"/>
       <c r="C10" s="5" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId3"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="12.42578125" customWidth="1"/>
-    <col min="2" max="2" width="11.140625" customWidth="1"/>
-    <col min="3" max="3" width="18.7109375" customWidth="1"/>
-    <col min="4" max="4" width="20.7109375" customWidth="1"/>
-    <col min="5" max="5" width="18" customWidth="1"/>
-    <col min="6" max="6" width="17.42578125" customWidth="1"/>
-    <col min="7" max="7" width="22.5703125" customWidth="1"/>
+    <col customWidth="1" min="1" max="1" width="12.5"/>
+    <col customWidth="1" min="2" max="2" width="11.13"/>
+    <col customWidth="1" min="3" max="3" width="18.75"/>
+    <col customWidth="1" min="4" max="4" width="20.75"/>
+    <col customWidth="1" min="5" max="5" width="18.0"/>
+    <col customWidth="1" min="6" max="6" width="17.38"/>
+    <col customWidth="1" min="7" max="7" width="22.63"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" s="5" t="s">
         <v>11</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C2" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="C3" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="C14" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="E2" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A3" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A4" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A5" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A6" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="C6" s="5" t="s">
+      <c r="D14" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B15" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="D6" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A7" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A8" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A9" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A10" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A11" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="G11" s="5" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A12" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>187</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="G12" s="5" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A13" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>192</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="G13" s="5" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A14" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>196</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>197</v>
-      </c>
-      <c r="F14" s="5" t="s">
-        <v>198</v>
-      </c>
-      <c r="G14" s="5" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A15" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>155</v>
-      </c>
       <c r="C15" s="5" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="16">
       <c r="A16" s="5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="17">
       <c r="A17" s="5" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="18">
       <c r="A18" s="5" t="s">
         <v>14</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="19">
       <c r="A19" s="5" t="s">
         <v>16</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="20">
       <c r="A20" s="5" t="s">
         <v>18</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="21">
       <c r="A21" s="5" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="22">
       <c r="A22" s="5" t="s">
         <v>13</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C22" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="G22" s="5" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B23" s="5" t="s">
         <v>238</v>
       </c>
-      <c r="D22" s="5" t="s">
-        <v>239</v>
-      </c>
-      <c r="E22" s="5" t="s">
-        <v>240</v>
-      </c>
-      <c r="F22" s="5" t="s">
-        <v>241</v>
-      </c>
-      <c r="G22" s="5" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A23" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>237</v>
-      </c>
       <c r="C23" s="5" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="24">
       <c r="A24" s="5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="25">
       <c r="A25" s="5" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="26">
       <c r="A26" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="27">
       <c r="A27" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C27" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="G27" s="5" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>269</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="F28" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="G28" s="5" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>274</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>275</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>276</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="G29" s="5" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="F30" s="5" t="s">
+        <v>282</v>
+      </c>
+      <c r="G30" s="5" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>284</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>285</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>287</v>
+      </c>
+      <c r="G31" s="5" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>290</v>
+      </c>
+      <c r="E32" s="5" t="s">
+        <v>291</v>
+      </c>
+      <c r="F32" s="5" t="s">
+        <v>292</v>
+      </c>
+      <c r="G32" s="5" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="B33" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="D27" s="5" t="s">
-        <v>264</v>
-      </c>
-      <c r="E27" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="F27" s="5" t="s">
-        <v>266</v>
-      </c>
-      <c r="G27" s="5" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A28" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>268</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>269</v>
-      </c>
-      <c r="E28" s="5" t="s">
-        <v>270</v>
-      </c>
-      <c r="F28" s="5" t="s">
-        <v>271</v>
-      </c>
-      <c r="G28" s="5" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A29" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>273</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>274</v>
-      </c>
-      <c r="E29" s="5" t="s">
-        <v>275</v>
-      </c>
-      <c r="F29" s="5" t="s">
-        <v>276</v>
-      </c>
-      <c r="G29" s="5" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A30" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="C30" s="5" t="s">
-        <v>278</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>279</v>
-      </c>
-      <c r="E30" s="5" t="s">
-        <v>280</v>
-      </c>
-      <c r="F30" s="5" t="s">
-        <v>281</v>
-      </c>
-      <c r="G30" s="5" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A31" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="C31" s="5" t="s">
-        <v>283</v>
-      </c>
-      <c r="D31" s="5" t="s">
-        <v>284</v>
-      </c>
-      <c r="E31" s="5" t="s">
-        <v>285</v>
-      </c>
-      <c r="F31" s="5" t="s">
-        <v>286</v>
-      </c>
-      <c r="G31" s="5" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A32" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>288</v>
-      </c>
-      <c r="D32" s="5" t="s">
-        <v>289</v>
-      </c>
-      <c r="E32" s="5" t="s">
-        <v>290</v>
-      </c>
-      <c r="F32" s="5" t="s">
-        <v>291</v>
-      </c>
-      <c r="G32" s="5" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A33" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>134</v>
-      </c>
       <c r="C33" s="3" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="34">
       <c r="A34" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="35">
       <c r="A35" s="3" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="36">
       <c r="A36" s="3" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="37">
       <c r="A37" s="3" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId3"/>
   </tableParts>
 </worksheet>
 </file>